--- a/data/export/2026-09-26-浦东35路.xlsx
+++ b/data/export/2026-09-26-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AC21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -826,7 +826,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1381,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1492,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1603,1228 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-26-浦东35路.xlsx
+++ b/data/export/2026-09-26-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC21"/>
+  <dimension ref="A1:AC32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,33 +693,37 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -776,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -815,7 +823,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -826,7 +834,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -854,32 +862,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -887,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -911,17 +923,17 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -931,13 +943,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -965,32 +981,36 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -998,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1022,33 +1042,37 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1159,7 +1183,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1244,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1294,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1355,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1405,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1466,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1516,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1577,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1627,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1688,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1714,7 +1738,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1799,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1825,7 +1849,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1910,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1936,7 +1960,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1997,7 +2021,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2047,7 +2071,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2132,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2158,7 +2182,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2243,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2269,7 +2293,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2354,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2380,7 +2404,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2465,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2491,7 +2515,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2576,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2602,7 +2626,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2687,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2713,7 +2737,7 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2721,22 +2745,22 @@
       <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2769,12 +2793,12 @@
       <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2824,7 +2848,1236 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>2/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>3/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-26-浦东35路.xlsx
+++ b/data/export/2026-09-26-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC32"/>
+  <dimension ref="A1:AC33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,7 +436,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
@@ -446,10 +446,10 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -991,24 +991,24 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1067,12 +1067,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -1100,32 +1100,36 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1133,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1157,17 +1161,17 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
@@ -1177,13 +1181,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1322,32 +1330,36 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1355,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1379,17 +1391,17 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
@@ -1399,13 +1411,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1482,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1577,7 +1593,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1688,7 +1704,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1799,7 +1815,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1877,12 +1893,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq40，推进2站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1910,7 +1926,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1918,10 +1934,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr"/>
-      <c r="R13" s="2" t="inlineStr"/>
-      <c r="S13" s="2" t="inlineStr"/>
-      <c r="T13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>08:02</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±4分钟；反向位置物理seq38（站名待映射） ETA 24分钟参与校验</t>
+        </is>
+      </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
           <t>07:12</t>
@@ -2021,7 +2053,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2132,7 +2164,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2354,7 +2386,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2465,7 +2497,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2576,7 +2608,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2687,7 +2719,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2798,7 +2830,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3020,7 +3052,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3131,7 +3163,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3242,7 +3274,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3353,7 +3385,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3464,7 +3496,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3575,7 +3607,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3686,7 +3718,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3740,7 +3772,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -3801,7 +3833,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3912,7 +3944,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -3970,22 +4002,22 @@
       <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4023,7 +4055,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4072,12 +4104,127 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>1/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>4/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-26-浦东35路.xlsx
+++ b/data/export/2026-09-26-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC33"/>
+  <dimension ref="A1:AC41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -834,7 +834,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,14 +1176,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
           <t>125.0</t>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -1219,32 +1219,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -1252,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1276,33 +1280,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -1340,24 +1348,24 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1367,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1406,22 +1414,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1449,32 +1457,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -1482,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1506,33 +1518,37 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1593,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1632,7 +1648,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1643,7 +1659,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -1671,32 +1687,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -1704,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1728,17 +1748,17 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
@@ -1748,13 +1768,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -1782,32 +1806,36 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -1815,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1839,33 +1867,37 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1930,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq40，推进2站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq62，推进24站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1926,7 +1958,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1992,7 +2024,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2020,32 +2052,36 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -2053,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2077,17 +2113,17 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
@@ -2097,13 +2133,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -2131,32 +2171,36 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -2164,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2188,33 +2232,37 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -2242,12 +2290,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq39推进至seq53，推进14站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2275,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2283,10 +2331,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q16" s="2" t="inlineStr"/>
-      <c r="R16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>物理seq23（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>08:16</t>
+        </is>
+      </c>
       <c r="S16" s="2" t="inlineStr"/>
-      <c r="T16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq23映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
           <t>07:24</t>
@@ -2325,7 +2385,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2436,7 +2496,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2497,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2547,7 +2607,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2608,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2658,7 +2718,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2719,7 +2779,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2769,7 +2829,7 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2830,7 +2890,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2880,7 +2940,7 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2991,7 +3051,7 @@
       <c r="AB22" s="2" t="inlineStr"/>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3052,7 +3112,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3102,7 +3162,7 @@
       <c r="AB23" s="2" t="inlineStr"/>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3163,7 +3223,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3213,7 +3273,7 @@
       <c r="AB24" s="2" t="inlineStr"/>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3274,7 +3334,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3324,7 +3384,7 @@
       <c r="AB25" s="2" t="inlineStr"/>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3385,7 +3445,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3435,7 +3495,7 @@
       <c r="AB26" s="2" t="inlineStr"/>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3556,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3546,7 +3606,7 @@
       <c r="AB27" s="2" t="inlineStr"/>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3607,7 +3667,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3657,7 +3717,7 @@
       <c r="AB28" s="2" t="inlineStr"/>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3718,7 +3778,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3772,7 +3832,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3893,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3883,7 +3943,7 @@
       <c r="AB30" s="2" t="inlineStr"/>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3944,7 +4004,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -3994,7 +4054,7 @@
       <c r="AB31" s="2" t="inlineStr"/>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4115,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4109,7 +4169,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -4170,7 +4230,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4224,7 +4284,919 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>9/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>5/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>10/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>1/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>11/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A79307D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>5/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>1/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-26-浦东35路.xlsx
+++ b/data/export/2026-09-26-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC41"/>
+  <dimension ref="A1:AC49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1763,14 +1763,14 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
           <t>128.0</t>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq39推进至seq53，推进14站，达到≥2站确认条件</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq39推进至seq59，推进20站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2524,32 +2524,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -2557,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2581,33 +2585,37 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -2635,32 +2643,36 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -2668,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2692,33 +2704,37 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -2746,32 +2762,36 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -2779,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2803,33 +2823,37 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -2857,32 +2881,36 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -2890,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2914,33 +2942,37 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -3079,32 +3111,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -3112,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3136,33 +3172,37 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -3190,32 +3230,36 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3223,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3247,17 +3291,17 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -3267,13 +3311,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3301,32 +3349,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3334,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3358,17 +3410,17 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
@@ -3378,13 +3430,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB25" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -3445,7 +3501,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3556,7 +3612,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3667,7 +3723,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3778,7 +3834,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3832,7 +3888,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -3893,7 +3949,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4004,7 +4060,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4115,7 +4171,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4230,7 +4286,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4284,7 +4340,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -4345,7 +4401,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4460,7 +4516,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4514,7 +4570,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -4575,7 +4631,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4690,7 +4746,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4744,7 +4800,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -4805,7 +4861,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4916,7 +4972,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5027,7 +5083,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5089,22 +5145,22 @@
       <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -5137,12 +5193,12 @@
       <c r="M41" s="2" t="inlineStr"/>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5191,12 +5247,928 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>9/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
           <t>124.0</t>
         </is>
       </c>
-      <c r="AC41" s="2" t="inlineStr">
+      <c r="AC42" s="2" t="inlineStr">
         <is>
           <t>1/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>1/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>5/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr"/>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>12/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>8/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>18/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>16/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-26-浦东35路.xlsx
+++ b/data/export/2026-09-26-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC49"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -828,13 +828,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -899,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -943,17 +947,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>124.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1057,22 +1061,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,22 +1180,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1300,7 +1304,7 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
@@ -1375,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1419,17 +1423,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1533,7 +1537,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1548,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1724,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1778,7 +1782,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1897,7 +1901,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2208,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2446,7 +2450,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2561,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2615,7 +2619,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2734,7 +2738,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2853,7 +2857,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2972,7 +2976,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3202,7 +3206,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -3321,7 +3325,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -3440,7 +3444,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3540,7 +3544,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3579,32 +3583,36 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3612,7 +3620,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3636,17 +3644,17 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
@@ -3656,13 +3664,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB27" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -3690,32 +3702,36 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3723,7 +3739,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3747,33 +3763,37 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -3801,32 +3821,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3834,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3858,37 +3882,37 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -3916,32 +3940,36 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3949,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3973,17 +4001,17 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -3993,13 +4021,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB30" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -4027,32 +4059,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -4060,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4084,17 +4120,17 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -4104,13 +4140,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB31" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -4138,32 +4178,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4171,7 +4215,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4195,17 +4239,17 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
@@ -4215,17 +4259,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>124.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -4253,32 +4297,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4286,7 +4334,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4310,37 +4358,37 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -4368,32 +4416,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4401,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4425,37 +4477,37 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -4483,32 +4535,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4516,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4540,17 +4596,17 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
@@ -4560,17 +4616,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -4598,32 +4654,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -4631,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4655,17 +4715,17 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4675,7 +4735,7 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
@@ -4746,7 +4806,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4785,7 +4845,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4800,7 +4860,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -4828,12 +4888,12 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程33%处后消失；随后反向物理轨迹由seq38推进至seq49，推进11站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -4861,7 +4921,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4869,10 +4929,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q38" s="2" t="inlineStr"/>
-      <c r="R38" s="2" t="inlineStr"/>
-      <c r="S38" s="2" t="inlineStr"/>
-      <c r="T38" s="2" t="inlineStr"/>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>物理seq22（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq22映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±5分钟；反向位置物理seq38（站名待映射） ETA 8分钟参与校验</t>
+        </is>
+      </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
           <t>09:38</t>
@@ -4972,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5083,7 +5159,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5137,7 +5213,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5274,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5252,7 +5328,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -5313,7 +5389,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5428,7 +5504,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5543,7 +5619,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5597,7 +5673,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5734,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5769,7 +5845,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5823,7 +5899,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5960,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5938,7 +6014,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -5999,7 +6075,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6053,7 +6129,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6190,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6168,7 +6244,693 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>20/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr"/>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>9/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>17/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>129.5</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>15/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>125.5</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>8/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>20/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-26-浦东35路.xlsx
+++ b/data/export/2026-09-26-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC55"/>
+  <dimension ref="A1:AC61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1542,17 +1542,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1652,18 +1652,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1772,7 +1776,7 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
@@ -1847,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1962,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,7 +2021,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2093,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2132,14 +2136,14 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
           <t>124.0</t>
@@ -2147,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2266,7 +2270,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2378,7 +2382,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2450,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2494,13 +2498,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2609,17 +2617,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2728,17 +2736,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -2803,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2842,7 +2850,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2922,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2976,7 +2984,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3206,7 +3214,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -3325,7 +3333,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3739,7 +3747,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3858,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3912,7 +3920,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4039,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -4150,7 +4158,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4388,7 +4396,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -4453,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4507,7 +4515,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4634,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -4664,24 +4672,24 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4691,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4740,7 +4748,7 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4773,32 +4781,36 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -4806,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4830,17 +4842,17 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
@@ -4850,17 +4862,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -4893,7 +4905,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程33%处后消失；随后反向物理轨迹由seq38推进至seq49，推进11站，达到≥2站确认条件</t>
+          <t>原方向在全程33%处后消失；随后反向物理轨迹由seq38推进至seq58，推进20站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -4921,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4976,7 +4988,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -5015,32 +5027,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -5048,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5072,33 +5088,37 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB39" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5241,32 +5261,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -5274,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5298,17 +5322,17 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -5318,7 +5342,7 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
@@ -5389,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5443,7 +5467,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -5471,32 +5495,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -5504,7 +5532,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5528,29 +5556,29 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
           <t>124.0</t>
@@ -5558,7 +5586,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -5586,32 +5614,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5619,7 +5651,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5643,17 +5675,17 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -5663,17 +5695,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -5701,32 +5733,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5734,7 +5770,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5758,17 +5794,17 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -5778,13 +5814,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB45" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -5812,32 +5852,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -5845,7 +5889,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5869,17 +5913,17 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
@@ -5889,17 +5933,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -5960,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5999,7 +6043,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6075,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6129,7 +6173,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -6190,7 +6234,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6244,7 +6288,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -6305,7 +6349,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6416,7 +6460,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6531,7 +6575,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6585,7 +6629,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -6646,7 +6690,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6700,7 +6744,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6761,7 +6805,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6815,7 +6859,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6876,7 +6920,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6920,17 +6964,695 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>135.5</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>21/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A79307D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr"/>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB55" s="2" t="inlineStr">
-        <is>
-          <t>137.0</t>
-        </is>
-      </c>
-      <c r="AC55" s="2" t="inlineStr">
-        <is>
-          <t>20/29</t>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>15/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr"/>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>2/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr"/>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>9/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-26-浦东35路.xlsx
+++ b/data/export/2026-09-26-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC61"/>
+  <dimension ref="A1:AC66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1066,17 +1066,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>127.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2612,14 +2612,14 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
           <t>126.5</t>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2855,17 +2855,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2974,17 +2974,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3199,22 +3199,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3557,13 +3557,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB26" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -3682,7 +3686,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -3747,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3786,22 +3790,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3905,7 +3909,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -4039,7 +4043,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4281,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4386,17 +4390,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>127.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4515,7 +4519,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4822,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4872,7 +4876,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5064,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5118,7 +5122,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -5233,7 +5237,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -5532,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5651,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5690,14 +5694,14 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
           <t>126.5</t>
@@ -5705,7 +5709,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5747,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
@@ -5770,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5819,7 +5823,7 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5862,24 +5866,24 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5889,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5938,7 +5942,7 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -5971,32 +5975,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>121分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -6004,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6028,17 +6036,17 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
@@ -6048,17 +6056,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -6086,32 +6094,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -6119,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6143,17 +6155,17 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
@@ -6163,17 +6175,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -6201,32 +6213,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -6234,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6258,37 +6274,37 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -6316,32 +6332,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -6349,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6373,17 +6393,17 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
@@ -6393,13 +6413,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB50" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -6427,32 +6451,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6460,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6484,37 +6512,37 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6575,7 +6603,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6614,7 +6642,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6657,32 +6685,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6690,7 +6722,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6714,17 +6746,17 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
@@ -6734,17 +6766,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>127.3</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -6805,7 +6837,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6859,7 +6891,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -6920,7 +6952,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6974,7 +7006,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -7035,7 +7067,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7146,7 +7178,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7200,7 +7232,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -7261,7 +7293,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7372,7 +7404,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7487,7 +7519,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7598,7 +7630,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7642,17 +7674,592 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>2/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>126.5</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>9/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>20/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>18/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>128.5</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>14/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB61" s="2" t="inlineStr">
-        <is>
-          <t>127.0</t>
-        </is>
-      </c>
-      <c r="AC61" s="2" t="inlineStr">
-        <is>
-          <t>9/29</t>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>12/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-26-浦东35路.xlsx
+++ b/data/export/2026-09-26-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC66"/>
+  <dimension ref="A1:AC70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>127.3</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>127.3</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,14 +1418,14 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
           <t>131.0</t>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1537,22 +1537,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3914,17 +3914,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4385,22 +4385,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>127.3</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4509,17 +4509,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>127.3</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4623,14 +4623,14 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
           <t>131.0</t>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4861,22 +4861,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5709,7 +5709,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -5947,7 +5947,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6461,24 +6461,24 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6537,7 +6537,7 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6570,32 +6570,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6603,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6627,17 +6631,17 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6647,17 +6651,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -6695,24 +6699,24 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>123分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6722,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6761,22 +6765,22 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>127.3</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -6804,32 +6808,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6837,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6861,17 +6869,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6881,17 +6889,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>127.3</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -6919,32 +6927,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -6952,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6976,37 +6988,37 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7046,12 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq46，推进8站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -7067,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7075,10 +7087,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q56" s="2" t="inlineStr"/>
-      <c r="R56" s="2" t="inlineStr"/>
-      <c r="S56" s="2" t="inlineStr"/>
-      <c r="T56" s="2" t="inlineStr"/>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="T56" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±5分钟；反向位置物理seq38（站名待映射） ETA 8分钟参与校验</t>
+        </is>
+      </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
           <t>12:28</t>
@@ -7178,7 +7206,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7293,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7404,7 +7432,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7519,7 +7547,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7630,7 +7658,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7745,7 +7773,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7799,7 +7827,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7888,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7975,7 +8003,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8019,17 +8047,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -8090,7 +8118,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8139,7 +8167,7 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8205,7 +8233,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8259,7 +8287,467 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>128.3</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>13/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>22/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>133.3</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>21/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>19/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-26-浦东35路.xlsx
+++ b/data/export/2026-09-26-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC70"/>
+  <dimension ref="A1:AC71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1190,12 +1190,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>127.3</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2021,18 +2021,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2101,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2331,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2508,7 +2512,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2577,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2627,7 +2631,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2815,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2984,7 +2988,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3164,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3214,7 +3218,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -3333,7 +3337,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3402,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3452,7 +3456,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -3567,7 +3571,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -3686,7 +3690,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3805,7 +3809,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3924,7 +3928,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4281,7 +4285,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4400,7 +4404,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4514,12 +4518,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>127.3</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4588,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4638,7 +4642,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -4822,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4871,12 +4875,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5068,7 +5072,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5122,7 +5126,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -5237,7 +5241,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -5356,7 +5360,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5655,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5709,7 +5713,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5832,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6185,7 +6189,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6304,7 +6308,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -6423,7 +6427,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6492,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6542,7 +6546,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -6607,7 +6611,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6661,7 +6665,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6730,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6780,7 +6784,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6818,24 +6822,24 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6845,7 +6849,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6894,12 +6898,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>127.3</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -6937,12 +6941,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
@@ -6964,7 +6968,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7013,12 +7017,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -7051,7 +7055,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq46，推进8站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq54，推进16站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -7079,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7206,7 +7210,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7260,7 +7264,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -7288,32 +7292,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -7321,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7345,33 +7353,37 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB58" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -7432,7 +7444,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7547,7 +7559,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7658,7 +7670,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7773,7 +7785,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7827,7 +7839,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -7888,7 +7900,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7942,7 +7954,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -8003,7 +8015,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8057,7 +8069,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -8118,7 +8130,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8172,7 +8184,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -8233,7 +8245,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8287,7 +8299,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -8348,7 +8360,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8402,7 +8414,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -8463,7 +8475,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8578,7 +8590,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8627,12 +8639,12 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -8693,7 +8705,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8747,7 +8759,122 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>2/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-26-浦东35路.xlsx
+++ b/data/export/2026-09-26-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC71"/>
+  <dimension ref="A1:AC76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1657,17 +1657,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2145,17 +2145,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>125.3</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2391,13 +2391,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2516,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -2577,7 +2581,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2621,17 +2625,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>125.7</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -2750,7 +2754,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -2815,7 +2819,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2859,17 +2863,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2992,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3218,7 +3222,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3322,14 +3326,14 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
           <t>130.0</t>
@@ -3337,7 +3341,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -3402,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3456,7 +3460,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -3571,7 +3575,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3675,14 +3679,14 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
           <t>127.0</t>
@@ -3690,7 +3694,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3759,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3809,7 +3813,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3928,7 +3932,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -3993,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4047,7 +4051,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -4285,7 +4289,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4404,7 +4408,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -4523,7 +4527,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -4588,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4826,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4880,7 +4884,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -4941,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4996,7 +5000,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -5072,7 +5076,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5116,17 +5120,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5226,7 +5230,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5241,7 +5245,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -5360,7 +5364,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5460,7 +5464,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5540,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5584,17 +5588,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>125.3</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5703,17 +5707,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>125.7</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -5832,7 +5836,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -5951,7 +5955,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -6016,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6060,17 +6064,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -6189,7 +6193,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6308,7 +6312,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -6427,7 +6431,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6546,7 +6550,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -6611,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6665,7 +6669,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -6730,7 +6734,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6784,7 +6788,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -6903,7 +6907,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6972,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7022,7 +7026,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -7055,7 +7059,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq54，推进16站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq59，推进21站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -7083,7 +7087,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7138,7 +7142,7 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7177,32 +7181,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -7210,7 +7218,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7234,17 +7242,17 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -7254,17 +7262,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -7302,24 +7310,24 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -7329,7 +7337,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7378,12 +7386,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -7411,32 +7419,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7444,7 +7456,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7468,17 +7480,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7488,17 +7500,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>125.3</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -7526,32 +7538,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -7559,7 +7575,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7583,17 +7599,17 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
@@ -7603,13 +7619,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB60" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -7637,32 +7657,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -7670,7 +7694,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7694,17 +7718,17 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
@@ -7714,17 +7738,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -7752,32 +7776,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -7785,7 +7813,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7809,17 +7837,17 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
@@ -7829,17 +7857,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>125.7</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -7900,7 +7928,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7954,7 +7982,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -8015,7 +8043,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8069,7 +8097,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -8130,7 +8158,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8184,7 +8212,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8273,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8299,7 +8327,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8388,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8414,7 +8442,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -8475,7 +8503,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8529,7 +8557,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -8590,7 +8618,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8644,7 +8672,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -8705,7 +8733,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8767,22 +8795,22 @@
       <c r="A71" s="2" t="inlineStr"/>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A79307D</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -8815,12 +8843,12 @@
       <c r="M71" s="2" t="inlineStr"/>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8834,45 +8862,616 @@
       <c r="T71" s="2" t="inlineStr"/>
       <c r="U71" s="2" t="inlineStr">
         <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr"/>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
           <t>15:25</t>
         </is>
       </c>
-      <c r="V71" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W71" s="2" t="inlineStr">
+      <c r="W72" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X71" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y71" s="2" t="inlineStr">
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z71" s="2" t="inlineStr">
+      <c r="Z72" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA71" s="2" t="inlineStr">
+      <c r="AA72" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB71" s="2" t="inlineStr">
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>9/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>5/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>18/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>9/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
         <is>
           <t>124.0</t>
         </is>
       </c>
-      <c r="AC71" s="2" t="inlineStr">
+      <c r="AC76" s="2" t="inlineStr">
         <is>
           <t>2/29</t>
         </is>

--- a/data/export/2026-09-26-浦东35路.xlsx
+++ b/data/export/2026-09-26-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC76"/>
+  <dimension ref="A1:AC82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -828,17 +828,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1066,17 +1066,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>128.3</t>
+          <t>127.8</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,14 +1180,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
           <t>126.0</t>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>125.7</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2739,14 +2739,14 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
           <t>134.0</t>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3212,17 +3212,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3450,17 +3450,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4041,17 +4041,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4398,17 +4398,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>128.3</t>
+          <t>127.8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4512,14 +4512,14 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
           <t>126.0</t>
@@ -4527,7 +4527,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5130,7 +5130,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>125.7</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5940,14 +5940,14 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
           <t>134.0</t>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6302,17 +6302,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6540,7 +6540,7 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
@@ -6550,7 +6550,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6659,7 +6659,7 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
@@ -6669,7 +6669,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6778,17 +6778,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>128.3</t>
+          <t>127.8</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6892,14 +6892,14 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
           <t>126.0</t>
@@ -6907,7 +6907,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6972,7 +6972,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7272,7 +7272,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -7337,7 +7337,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7614,7 +7614,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
@@ -7813,7 +7813,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7862,12 +7862,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>125.7</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -7895,32 +7895,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -7928,7 +7932,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7952,17 +7956,17 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
@@ -7972,17 +7976,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -8010,32 +8014,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8043,7 +8051,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8067,17 +8075,17 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
@@ -8087,7 +8095,7 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
@@ -8097,7 +8105,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -8125,32 +8133,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8158,7 +8170,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8182,17 +8194,17 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
@@ -8202,7 +8214,7 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
@@ -8212,7 +8224,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -8240,32 +8252,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8273,7 +8289,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8297,17 +8313,17 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
@@ -8317,17 +8333,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -8355,32 +8371,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8388,7 +8408,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8412,17 +8432,17 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
@@ -8432,17 +8452,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>128.3</t>
+          <t>127.8</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -8470,32 +8490,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8503,7 +8527,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8527,17 +8551,17 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
@@ -8547,17 +8571,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -8618,7 +8642,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8733,7 +8757,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8787,7 +8811,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -8848,7 +8872,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8959,7 +8983,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9074,7 +9098,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9189,7 +9213,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9243,7 +9267,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -9304,7 +9328,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9419,7 +9443,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9477,6 +9501,696 @@
         </is>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>9/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>24/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>124.5</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>4/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>26/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>1/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>7/29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-09-26-浦东35路.xlsx
+++ b/data/export/2026-09-26-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC82"/>
+  <dimension ref="A1:AC89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>127.8</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,14 +1771,14 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
           <t>128.0</t>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1895,17 +1895,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2140,14 +2140,14 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
           <t>125.3</t>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2858,14 +2858,14 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
           <t>127.0</t>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3445,22 +3445,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -3932,7 +3932,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>127.8</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4636,17 +4636,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5115,7 +5115,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5235,17 +5235,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5349,14 +5349,14 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
           <t>128.0</t>
@@ -5364,7 +5364,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5583,14 +5583,14 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
           <t>125.3</t>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -5717,7 +5717,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5821,7 +5821,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6059,14 +6059,14 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
           <t>127.0</t>
@@ -6074,7 +6074,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -6312,7 +6312,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6669,7 +6669,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6783,12 +6783,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>127.8</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6907,7 +6907,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -6972,7 +6972,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7026,7 +7026,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -7087,7 +7087,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7218,7 +7218,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7257,7 +7257,7 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7337,7 +7337,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -7456,7 +7456,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7495,14 +7495,14 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA59" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
           <t>125.3</t>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -7694,7 +7694,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7733,14 +7733,14 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
           <t>127.0</t>
@@ -7748,7 +7748,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -7867,7 +7867,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -8105,7 +8105,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -8252,36 +8252,32 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8289,7 +8285,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8313,37 +8309,37 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -8381,24 +8377,24 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -8408,7 +8404,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8457,12 +8453,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>127.8</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -8500,24 +8496,24 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -8527,7 +8523,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8566,7 +8562,7 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
@@ -8576,12 +8572,12 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -8642,7 +8638,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8696,7 +8692,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -8724,32 +8720,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8757,7 +8757,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8781,17 +8781,17 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
@@ -8801,17 +8801,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -8839,12 +8839,12 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq63，推进25站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -8872,7 +8872,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8880,10 +8880,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q71" s="2" t="inlineStr"/>
-      <c r="R71" s="2" t="inlineStr"/>
-      <c r="S71" s="2" t="inlineStr"/>
-      <c r="T71" s="2" t="inlineStr"/>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="S71" s="2" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="T71" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±3分钟；反向位置物理seq38（站名待映射） ETA 8分钟参与校验</t>
+        </is>
+      </c>
       <c r="U71" s="2" t="inlineStr">
         <is>
           <t>15:22</t>
@@ -8983,7 +8999,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9037,7 +9053,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -9065,32 +9081,36 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -9098,7 +9118,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9122,17 +9142,17 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
@@ -9142,17 +9162,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -9213,7 +9233,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9267,7 +9287,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -9328,7 +9348,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9382,7 +9402,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -9443,7 +9463,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9558,7 +9578,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9612,7 +9632,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -9673,7 +9693,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9727,7 +9747,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -9788,7 +9808,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9903,7 +9923,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10018,7 +10038,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10080,22 +10100,22 @@
       <c r="A82" s="2" t="inlineStr"/>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -10128,12 +10148,12 @@
       <c r="M82" s="2" t="inlineStr"/>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10172,22 +10192,827 @@
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>12/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA82" s="2" t="inlineStr">
+      <c r="AA83" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB82" s="2" t="inlineStr">
+      <c r="AB83" s="2" t="inlineStr">
         <is>
           <t>126.0</t>
         </is>
       </c>
-      <c r="AC82" s="2" t="inlineStr">
-        <is>
-          <t>7/29</t>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>6/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>21/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>12/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>125.3</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>5/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>15/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>130.5</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>20/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>8/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-26-浦东35路.xlsx
+++ b/data/export/2026-09-26-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC89"/>
+  <dimension ref="A1:AC97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,14 +1418,14 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
           <t>130.0</t>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1895,17 +1895,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2264,17 +2264,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2391,17 +2391,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       <c r="AB22" s="2" t="inlineStr"/>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3207,14 +3207,14 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
           <t>133.3</t>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3326,22 +3326,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3575,7 +3575,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3679,22 +3679,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -3813,7 +3813,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -3932,7 +3932,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4631,14 +4631,14 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
           <t>130.0</t>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -5011,7 +5011,7 @@
       <c r="AB38" s="2" t="inlineStr"/>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5130,7 +5130,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5235,17 +5235,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5469,17 +5469,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -5717,7 +5717,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -6193,7 +6193,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6297,14 +6297,14 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
           <t>133.3</t>
@@ -6312,7 +6312,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -6550,7 +6550,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -6669,7 +6669,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -6788,7 +6788,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6907,7 +6907,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -7087,7 +7087,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7142,7 +7142,7 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7153,7 +7153,7 @@
       <c r="AB56" s="2" t="inlineStr"/>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -7218,7 +7218,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7272,7 +7272,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -7337,7 +7337,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -7456,7 +7456,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7510,7 +7510,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7619,17 +7619,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -7694,7 +7694,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -7867,7 +7867,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -7932,7 +7932,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7971,14 +7971,14 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA63" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
           <t>133.3</t>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -8105,7 +8105,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -8224,7 +8224,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -8285,7 +8285,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8339,7 +8339,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -8458,7 +8458,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -8523,7 +8523,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8577,7 +8577,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -8692,7 +8692,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -8757,7 +8757,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8796,14 +8796,14 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA70" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
           <t>130.0</t>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -8872,7 +8872,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8927,7 +8927,7 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
@@ -8938,7 +8938,7 @@
       <c r="AB71" s="2" t="inlineStr"/>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -8999,7 +8999,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9038,7 +9038,7 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
@@ -9053,7 +9053,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -9081,36 +9081,32 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>145分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -9118,7 +9114,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9142,17 +9138,17 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
@@ -9162,17 +9158,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -9200,32 +9196,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9233,7 +9233,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9257,37 +9257,37 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA74" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -9315,32 +9315,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9348,7 +9352,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9372,37 +9376,37 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA75" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -9430,32 +9434,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -9463,7 +9471,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9487,17 +9495,17 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
@@ -9507,17 +9515,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -9545,32 +9553,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -9578,7 +9590,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9602,17 +9614,17 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
@@ -9622,17 +9634,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -9693,7 +9705,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9747,7 +9759,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -9808,7 +9820,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9862,7 +9874,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -9923,7 +9935,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9962,7 +9974,7 @@
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
@@ -9977,7 +9989,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10050,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10092,7 +10104,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -10153,7 +10165,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10207,7 +10219,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -10268,7 +10280,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10322,7 +10334,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -10383,7 +10395,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10437,7 +10449,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -10498,7 +10510,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10552,7 +10564,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -10613,7 +10625,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10667,7 +10679,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -10728,7 +10740,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10782,7 +10794,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -10843,7 +10855,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10897,7 +10909,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -10958,7 +10970,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11012,7 +11024,919 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>8/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>8/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A79307D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr"/>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>133.3</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>22/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>18/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>14/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr"/>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>26/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>135.5</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>25/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-26-浦东35路.xlsx
+++ b/data/export/2026-09-26-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC97"/>
+  <dimension ref="A1:AC101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3565,17 +3565,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5130,7 +5130,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6421,17 +6421,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -7026,7 +7026,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -7087,7 +7087,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7218,7 +7218,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7272,7 +7272,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -7337,7 +7337,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7456,7 +7456,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7614,7 +7614,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7932,7 +7932,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -8285,7 +8285,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8523,7 +8523,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8692,7 +8692,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -8757,7 +8757,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8872,7 +8872,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
@@ -9233,7 +9233,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9406,7 +9406,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -9471,7 +9471,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9510,7 +9510,7 @@
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
@@ -9590,7 +9590,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9629,7 +9629,7 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -9672,32 +9672,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -9705,7 +9709,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9729,17 +9733,17 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
@@ -9749,12 +9753,12 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
@@ -9820,7 +9824,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9859,7 +9863,7 @@
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
@@ -9902,32 +9906,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -9935,7 +9943,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9959,17 +9967,17 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
@@ -9979,17 +9987,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -10050,7 +10058,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10165,7 +10173,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10280,7 +10288,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10395,7 +10403,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10449,7 +10457,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -10510,7 +10518,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10625,7 +10633,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10740,7 +10748,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10855,7 +10863,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10970,7 +10978,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11085,7 +11093,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11200,7 +11208,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11311,7 +11319,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11365,7 +11373,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -11426,7 +11434,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11541,7 +11549,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11656,7 +11664,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11767,7 +11775,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11811,17 +11819,17 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -11882,7 +11890,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11936,7 +11944,467 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>4/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>128.5</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>13/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>124.5</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>3/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>129.5</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>17/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-26-浦东35路.xlsx
+++ b/data/export/2026-09-26-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC101"/>
+  <dimension ref="A1:AC103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2506,17 +2506,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2739,14 +2739,14 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
           <t>133.3</t>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3450,17 +3450,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3575,7 +3575,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -3813,7 +3813,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -3932,7 +3932,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5130,7 +5130,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5826,17 +5826,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5940,14 +5940,14 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
           <t>133.3</t>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -6550,7 +6550,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -6669,7 +6669,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -7087,7 +7087,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7218,7 +7218,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7272,7 +7272,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -7337,7 +7337,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7456,7 +7456,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -7694,7 +7694,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7932,7 +7932,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -8105,7 +8105,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -8224,7 +8224,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -8285,7 +8285,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8329,17 +8329,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -8523,7 +8523,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8577,7 +8577,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -8692,7 +8692,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -8757,7 +8757,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8811,7 +8811,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -8872,7 +8872,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9233,7 +9233,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9287,7 +9287,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -9352,7 +9352,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9406,7 +9406,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -9471,7 +9471,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9525,7 +9525,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -9590,7 +9590,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9644,7 +9644,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -9709,7 +9709,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9748,14 +9748,14 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA78" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
           <t>133.3</t>
@@ -9763,7 +9763,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -9824,7 +9824,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9997,7 +9997,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10097,7 +10097,7 @@
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA81" s="2" t="inlineStr">
@@ -10403,7 +10403,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10457,7 +10457,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -10485,32 +10485,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10518,7 +10522,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10542,17 +10546,17 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
@@ -10562,17 +10566,17 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -10633,7 +10637,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10715,32 +10719,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -10748,7 +10756,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10772,17 +10780,17 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
@@ -10792,17 +10800,17 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -10863,7 +10871,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10917,7 +10925,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -10978,7 +10986,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11093,7 +11101,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11208,7 +11216,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11319,7 +11327,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11373,7 +11381,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -11434,7 +11442,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11488,7 +11496,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -11549,7 +11557,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11603,7 +11611,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -11664,7 +11672,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11775,7 +11783,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11829,7 +11837,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -11890,7 +11898,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11944,7 +11952,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -12005,7 +12013,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12120,7 +12128,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12174,7 +12182,7 @@
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -12235,7 +12243,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12350,7 +12358,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12404,7 +12412,237 @@
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>15/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>133.3</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>22/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>1/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-26-浦东35路.xlsx
+++ b/data/export/2026-09-26-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC103"/>
+  <dimension ref="A1:AC105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -828,17 +828,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>125.3</t>
+          <t>125.8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2511,12 +2511,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2863,17 +2863,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>126.8</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3212,17 +3212,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>130.2</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3331,17 +3331,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3455,12 +3455,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3575,7 +3575,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -3813,7 +3813,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4041,17 +4041,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>125.3</t>
+          <t>125.8</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5821,7 +5821,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5831,12 +5831,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6064,17 +6064,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>126.8</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6302,17 +6302,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>130.2</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -6550,7 +6550,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -6788,7 +6788,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -7087,7 +7087,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -7456,7 +7456,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>125.3</t>
+          <t>125.8</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -7694,7 +7694,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7738,17 +7738,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>126.8</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -7932,7 +7932,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7976,17 +7976,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>130.2</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -8224,7 +8224,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -8285,7 +8285,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8334,12 +8334,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -8458,7 +8458,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -8523,7 +8523,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8567,17 +8567,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -8692,7 +8692,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -8757,7 +8757,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8872,7 +8872,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -9053,7 +9053,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -9114,7 +9114,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9233,7 +9233,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -9352,7 +9352,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9406,7 +9406,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -9471,7 +9471,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9590,7 +9590,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9644,7 +9644,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -9709,7 +9709,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9763,7 +9763,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -9824,7 +9824,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9997,7 +9997,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA82" s="2" t="inlineStr">
@@ -10227,7 +10227,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -10495,12 +10495,12 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>19:38</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
@@ -10522,7 +10522,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10571,12 +10571,12 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -10604,32 +10604,36 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -10637,7 +10641,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10661,17 +10665,17 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
@@ -10681,12 +10685,12 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>125.3</t>
+          <t>125.8</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
@@ -10729,24 +10733,24 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -10756,7 +10760,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10795,7 +10799,7 @@
       </c>
       <c r="Z87" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA87" s="2" t="inlineStr">
@@ -10805,12 +10809,12 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -10838,32 +10842,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10871,7 +10879,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10895,17 +10903,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10915,17 +10923,17 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -10953,32 +10961,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -10986,7 +10998,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11010,17 +11022,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -11030,17 +11042,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>126.8</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -11155,7 +11167,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -11183,12 +11195,12 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq38推进至seq57，推进19站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -11216,7 +11228,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11224,10 +11236,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q91" s="2" t="inlineStr"/>
-      <c r="R91" s="2" t="inlineStr"/>
-      <c r="S91" s="2" t="inlineStr"/>
-      <c r="T91" s="2" t="inlineStr"/>
+      <c r="Q91" s="2" t="inlineStr">
+        <is>
+          <t>物理seq23（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R91" s="2" t="inlineStr">
+        <is>
+          <t>19:07</t>
+        </is>
+      </c>
+      <c r="S91" s="2" t="inlineStr">
+        <is>
+          <t>19:14</t>
+        </is>
+      </c>
+      <c r="T91" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq23映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±7分钟；反向位置物理seq38（站名待映射） ETA 8分钟参与校验</t>
+        </is>
+      </c>
       <c r="U91" s="2" t="inlineStr">
         <is>
           <t>18:12</t>
@@ -11294,32 +11322,36 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>121分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -11327,7 +11359,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11351,17 +11383,17 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
@@ -11371,17 +11403,17 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>130.2</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -11442,7 +11474,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11524,32 +11556,36 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>121分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11557,7 +11593,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11581,17 +11617,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11601,17 +11637,17 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -11672,7 +11708,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11783,7 +11819,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11837,7 +11873,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -11898,7 +11934,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11952,7 +11988,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -12013,7 +12049,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12128,7 +12164,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12182,7 +12218,7 @@
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -12243,7 +12279,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12358,7 +12394,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12473,7 +12509,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12527,7 +12563,7 @@
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -12588,7 +12624,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12646,6 +12682,236 @@
         </is>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>11/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr"/>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr"/>
+      <c r="R105" s="2" t="inlineStr"/>
+      <c r="S105" s="2" t="inlineStr"/>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z105" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA105" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB105" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC105" s="2" t="inlineStr">
+        <is>
+          <t>21/30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-09-26-浦东35路.xlsx
+++ b/data/export/2026-09-26-浦东35路.xlsx
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>130.8</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1895,17 +1895,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2264,17 +2264,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>28/30</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>126.3</t>
+          <t>126.7</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4636,17 +4636,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>130.8</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5235,17 +5235,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5469,17 +5469,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -5717,7 +5717,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -6074,7 +6074,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -6193,7 +6193,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>28/30</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6669,7 +6669,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -6907,7 +6907,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -7272,7 +7272,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -7391,7 +7391,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -7867,7 +7867,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -8105,7 +8105,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -8339,7 +8339,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -8692,7 +8692,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -8757,7 +8757,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8801,17 +8801,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>130.8</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -9053,7 +9053,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -9114,7 +9114,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9158,17 +9158,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -9233,7 +9233,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9282,7 +9282,7 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>126.3</t>
+          <t>126.7</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9515,17 +9515,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -9590,7 +9590,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9763,7 +9763,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -9824,7 +9824,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10058,7 +10058,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10342,7 +10342,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -10457,7 +10457,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -10576,7 +10576,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -10760,7 +10760,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -10933,7 +10933,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -11052,7 +11052,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -11167,7 +11167,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -11441,32 +11441,36 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11474,7 +11478,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11498,17 +11502,17 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
@@ -11518,17 +11522,17 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>130.8</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -11566,24 +11570,24 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>121分钟</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -11593,7 +11597,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11642,7 +11646,7 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>126.3</t>
+          <t>126.7</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
@@ -11675,32 +11679,36 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>17:51</t>
@@ -11708,7 +11716,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11732,17 +11740,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11752,13 +11760,17 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB95" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -11786,12 +11798,12 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq60，推进32站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -11819,7 +11831,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11827,10 +11839,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q96" s="2" t="inlineStr"/>
-      <c r="R96" s="2" t="inlineStr"/>
-      <c r="S96" s="2" t="inlineStr"/>
-      <c r="T96" s="2" t="inlineStr"/>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>物理seq28（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R96" s="2" t="inlineStr">
+        <is>
+          <t>20:02</t>
+        </is>
+      </c>
+      <c r="S96" s="2" t="inlineStr">
+        <is>
+          <t>20:11</t>
+        </is>
+      </c>
+      <c r="T96" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq28映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U96" s="2" t="inlineStr">
         <is>
           <t>19:10</t>
@@ -11901,32 +11929,36 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:26</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11934,7 +11966,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11958,17 +11990,17 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -11978,12 +12010,12 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
@@ -12016,32 +12048,36 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:25</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -12049,7 +12085,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12073,17 +12109,17 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
@@ -12093,17 +12129,17 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -12164,7 +12200,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12279,7 +12315,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12361,32 +12397,36 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:49</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M101" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -12394,7 +12434,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12418,17 +12458,17 @@
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y101" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z101" s="2" t="inlineStr">
@@ -12438,17 +12478,17 @@
       </c>
       <c r="AA101" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -12509,7 +12549,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12563,7 +12603,7 @@
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -12624,7 +12664,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12739,7 +12779,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12854,7 +12894,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12908,7 +12948,7 @@
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
